--- a/clp/qualidade/tagPrensa.xlsx
+++ b/clp/qualidade/tagPrensa.xlsx
@@ -8,12 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\hostLinkOmron\hotsLinkOmron\clp\qualidade\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD38C513-A434-42DD-96B3-766EB474361F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1A1D2E2-6009-4B88-852C-DB99F465A584}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{4A80786E-FABD-419D-A196-A5DCFA0D7687}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{4A80786E-FABD-419D-A196-A5DCFA0D7687}"/>
   </bookViews>
   <sheets>
-    <sheet name="Planilha1" sheetId="1" r:id="rId1"/>
+    <sheet name="Prensa" sheetId="1" r:id="rId1"/>
+    <sheet name="Carga" sheetId="2" r:id="rId2"/>
+    <sheet name="Escolha41" sheetId="3" r:id="rId3"/>
+    <sheet name="Escolha43" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="357">
   <si>
     <t>BOOL</t>
   </si>
@@ -478,6 +481,636 @@
   </si>
   <si>
     <t>relogio interno</t>
+  </si>
+  <si>
+    <t>passo a passo formador fila entrada roler 41</t>
+  </si>
+  <si>
+    <t>sensor peças maquineta descarga 41</t>
+  </si>
+  <si>
+    <t>sensor sobre rolos entrada forno</t>
+  </si>
+  <si>
+    <t>rele espaco forno 17 (saida 3.03)</t>
+  </si>
+  <si>
+    <t>passo a passo formador fila entrada roler 42</t>
+  </si>
+  <si>
+    <t>status roller desc. 42</t>
+  </si>
+  <si>
+    <t>bancalino baixo carga forno 18</t>
+  </si>
+  <si>
+    <t>rele forno 18 (saida 3.03)</t>
+  </si>
+  <si>
+    <t>cnt de planos de carga 43</t>
+  </si>
+  <si>
+    <t>cnt de planos de descarga 43</t>
+  </si>
+  <si>
+    <t>bancalino entrada forno</t>
+  </si>
+  <si>
+    <t>rele forno 22</t>
+  </si>
+  <si>
+    <t>contagem de planos da carga carro</t>
+  </si>
+  <si>
+    <t>status roller C41</t>
+  </si>
+  <si>
+    <t>contador de gavetas carga roller mf42</t>
+  </si>
+  <si>
+    <t>contador descarga gaveta roller descarga mf42</t>
+  </si>
+  <si>
+    <t>contagem de planos da descarga carro</t>
+  </si>
+  <si>
+    <t>contagem peças roller carga 43</t>
+  </si>
+  <si>
+    <t>status roller C43</t>
+  </si>
+  <si>
+    <t>status roller D43</t>
+  </si>
+  <si>
+    <t>reset retorno peças</t>
+  </si>
+  <si>
+    <t>20.01</t>
+  </si>
+  <si>
+    <t>20.02</t>
+  </si>
+  <si>
+    <t>30.02</t>
+  </si>
+  <si>
+    <t>estoque vazio</t>
+  </si>
+  <si>
+    <t>30.04</t>
+  </si>
+  <si>
+    <t>estoque zero mf42</t>
+  </si>
+  <si>
+    <t>30.05</t>
+  </si>
+  <si>
+    <t>comparador planos  vazios</t>
+  </si>
+  <si>
+    <t>50.00</t>
+  </si>
+  <si>
+    <t>liga cnt10</t>
+  </si>
+  <si>
+    <t>50.01</t>
+  </si>
+  <si>
+    <t>reset cnt10</t>
+  </si>
+  <si>
+    <t>50.02</t>
+  </si>
+  <si>
+    <t>liga cnt11</t>
+  </si>
+  <si>
+    <t>50.03</t>
+  </si>
+  <si>
+    <t>reset cnt11</t>
+  </si>
+  <si>
+    <t>50.04</t>
+  </si>
+  <si>
+    <t>liga cnt12</t>
+  </si>
+  <si>
+    <t>50.05</t>
+  </si>
+  <si>
+    <t>reset cnt12</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>C0010</t>
+  </si>
+  <si>
+    <t>reset inicio turno 1</t>
+  </si>
+  <si>
+    <t>C0011</t>
+  </si>
+  <si>
+    <t>reset inicio turno 2</t>
+  </si>
+  <si>
+    <t>C0012</t>
+  </si>
+  <si>
+    <t>reset inicio turno 3</t>
+  </si>
+  <si>
+    <t>C43</t>
+  </si>
+  <si>
+    <t>contador de planos da 43</t>
+  </si>
+  <si>
+    <t>contador peças</t>
+  </si>
+  <si>
+    <t>D107</t>
+  </si>
+  <si>
+    <t>peças por fila entrada forno</t>
+  </si>
+  <si>
+    <t>Ano Relogio</t>
+  </si>
+  <si>
+    <t>Ano Relogio 4 Digitos</t>
+  </si>
+  <si>
+    <t>D300</t>
+  </si>
+  <si>
+    <t>D301</t>
+  </si>
+  <si>
+    <t>primeiro DM de contagem forno</t>
+  </si>
+  <si>
+    <t>peças por fila f17</t>
+  </si>
+  <si>
+    <t>peças por fila f18</t>
+  </si>
+  <si>
+    <t>peças por fila f22</t>
+  </si>
+  <si>
+    <t>primeiro DM envio roller</t>
+  </si>
+  <si>
+    <t>D500</t>
+  </si>
+  <si>
+    <t>turno 1,2,3</t>
+  </si>
+  <si>
+    <t>D518</t>
+  </si>
+  <si>
+    <t>D520</t>
+  </si>
+  <si>
+    <t>mês calendario</t>
+  </si>
+  <si>
+    <t>D3001</t>
+  </si>
+  <si>
+    <t>receita de destino RC43</t>
+  </si>
+  <si>
+    <t>D3800</t>
+  </si>
+  <si>
+    <t>receita de destino F22</t>
+  </si>
+  <si>
+    <t>D4001</t>
+  </si>
+  <si>
+    <t>H10.00</t>
+  </si>
+  <si>
+    <t>forno com espaço</t>
+  </si>
+  <si>
+    <t>H10.01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">status roller carga 41 </t>
+  </si>
+  <si>
+    <t>H10.02</t>
+  </si>
+  <si>
+    <t>H10.03</t>
+  </si>
+  <si>
+    <t>roller carga 42</t>
+  </si>
+  <si>
+    <t>H10.04</t>
+  </si>
+  <si>
+    <t>H10.05</t>
+  </si>
+  <si>
+    <t>status roller descarga 42</t>
+  </si>
+  <si>
+    <t>H10.06</t>
+  </si>
+  <si>
+    <t>roller descarga 41</t>
+  </si>
+  <si>
+    <t>H10.07</t>
+  </si>
+  <si>
+    <t>roller carga 43</t>
+  </si>
+  <si>
+    <t>H10.08</t>
+  </si>
+  <si>
+    <t>status roller descarga 43</t>
+  </si>
+  <si>
+    <t>H19.15</t>
+  </si>
+  <si>
+    <t>correção estoque IHM (mais)</t>
+  </si>
+  <si>
+    <t>Envia relogio superviório</t>
+  </si>
+  <si>
+    <t>H20.01</t>
+  </si>
+  <si>
+    <t>correção estoque IHM (menos)</t>
+  </si>
+  <si>
+    <t>H20.02</t>
+  </si>
+  <si>
+    <t>H20.03</t>
+  </si>
+  <si>
+    <t>H20.04</t>
+  </si>
+  <si>
+    <t>H20.05</t>
+  </si>
+  <si>
+    <t>H20.06</t>
+  </si>
+  <si>
+    <t>correcão estoque(menos)</t>
+  </si>
+  <si>
+    <t>H20.07</t>
+  </si>
+  <si>
+    <t>correcão estoque(mais)</t>
+  </si>
+  <si>
+    <t>H20.08</t>
+  </si>
+  <si>
+    <t>H20.09</t>
+  </si>
+  <si>
+    <t>H20.10</t>
+  </si>
+  <si>
+    <t>H20.11</t>
+  </si>
+  <si>
+    <t>filtro senso</t>
+  </si>
+  <si>
+    <t>passoFormFila41</t>
+  </si>
+  <si>
+    <t>passoFormFila42</t>
+  </si>
+  <si>
+    <t>pcRollerDesc41</t>
+  </si>
+  <si>
+    <t>ftcEspacoF17</t>
+  </si>
+  <si>
+    <t>ftcRolosForno17</t>
+  </si>
+  <si>
+    <t>statusRollerDesc42</t>
+  </si>
+  <si>
+    <t>bancBaixoF18</t>
+  </si>
+  <si>
+    <t>releF18</t>
+  </si>
+  <si>
+    <t>cntPlanosRollerCarga43</t>
+  </si>
+  <si>
+    <t>cntPlanosRollerDescarga43</t>
+  </si>
+  <si>
+    <t>bancEntradaForno22</t>
+  </si>
+  <si>
+    <t>releF22</t>
+  </si>
+  <si>
+    <t>statusRollerDesc41</t>
+  </si>
+  <si>
+    <t>statusRollerDesc43</t>
+  </si>
+  <si>
+    <t>peçaPorF17</t>
+  </si>
+  <si>
+    <t>peçaPorF18</t>
+  </si>
+  <si>
+    <t>peçaPorF22</t>
+  </si>
+  <si>
+    <t>cntPlanosCargaRoller42</t>
+  </si>
+  <si>
+    <t>cntPlanosRollerDescarga42</t>
+  </si>
+  <si>
+    <t>statusRollerCarg41</t>
+  </si>
+  <si>
+    <t>contPeçasCarga43</t>
+  </si>
+  <si>
+    <t>statusRollerCarga43</t>
+  </si>
+  <si>
+    <t>estoqueVazio42</t>
+  </si>
+  <si>
+    <t>ligaCnt10</t>
+  </si>
+  <si>
+    <t>resetCnt10</t>
+  </si>
+  <si>
+    <t>ligaCnt11</t>
+  </si>
+  <si>
+    <t>resetCnt11</t>
+  </si>
+  <si>
+    <t>ligaCnt12</t>
+  </si>
+  <si>
+    <t>resetCnt12</t>
+  </si>
+  <si>
+    <t>resetInicioT1</t>
+  </si>
+  <si>
+    <t>resetInicioT2</t>
+  </si>
+  <si>
+    <t>resetInicioT3</t>
+  </si>
+  <si>
+    <t>cntPlanos43</t>
+  </si>
+  <si>
+    <t>cntContPc</t>
+  </si>
+  <si>
+    <t>segRelogio</t>
+  </si>
+  <si>
+    <t>minRelogio</t>
+  </si>
+  <si>
+    <t>HoraRelogio</t>
+  </si>
+  <si>
+    <t>AnoRelógio4dit</t>
+  </si>
+  <si>
+    <t>firstDMforno</t>
+  </si>
+  <si>
+    <t>firstDMenvioRoller</t>
+  </si>
+  <si>
+    <t>turno1_2_3</t>
+  </si>
+  <si>
+    <t>_r_horas</t>
+  </si>
+  <si>
+    <t>_t_minutos</t>
+  </si>
+  <si>
+    <t>_d_segundos</t>
+  </si>
+  <si>
+    <t>diaCalend</t>
+  </si>
+  <si>
+    <t>filtroSen</t>
+  </si>
+  <si>
+    <t>mêsCalend</t>
+  </si>
+  <si>
+    <t>linhaSelecionada</t>
+  </si>
+  <si>
+    <t>receitaDestRolle43</t>
+  </si>
+  <si>
+    <t>receitaDestF22</t>
+  </si>
+  <si>
+    <t>HstatusRollerDesc41</t>
+  </si>
+  <si>
+    <t>HrollerC42</t>
+  </si>
+  <si>
+    <t>HstatusRollerDesc42</t>
+  </si>
+  <si>
+    <t>HrollerDesc41</t>
+  </si>
+  <si>
+    <t>HrollerCarg43</t>
+  </si>
+  <si>
+    <t>EnviRelogioSupervisorio</t>
+  </si>
+  <si>
+    <t>iniciaCntT2</t>
+  </si>
+  <si>
+    <t>iniciaCntT1</t>
+  </si>
+  <si>
+    <t>iniciaCntT3</t>
+  </si>
+  <si>
+    <t>cntPlanosCargaRoller41</t>
+  </si>
+  <si>
+    <t>cntPlanosDescRolle41</t>
+  </si>
+  <si>
+    <t>reseRetornoPc1</t>
+  </si>
+  <si>
+    <t>reseRetornoPc2</t>
+  </si>
+  <si>
+    <t>reseRetornoPc3</t>
+  </si>
+  <si>
+    <t>estoqueVazio41</t>
+  </si>
+  <si>
+    <t>estoqueVazio43</t>
+  </si>
+  <si>
+    <t>ponteiroDB22</t>
+  </si>
+  <si>
+    <t>fornoComEspacoF17</t>
+  </si>
+  <si>
+    <t>HfornComForno18</t>
+  </si>
+  <si>
+    <t>HfornoComEspacoF22</t>
+  </si>
+  <si>
+    <t>corrEstoqueIHM41</t>
+  </si>
+  <si>
+    <t>corrEstoqueIHMmenos41</t>
+  </si>
+  <si>
+    <t>corrEstoqueIHMmais42</t>
+  </si>
+  <si>
+    <t>corrEstoqueIHMmenos42</t>
+  </si>
+  <si>
+    <t>corrEstoqueIHMmais43</t>
+  </si>
+  <si>
+    <t>corrEstoqueIHMmenos43</t>
+  </si>
+  <si>
+    <t>corrEstoqueIHMmais41</t>
+  </si>
+  <si>
+    <t>corrEstoqueMenos41</t>
+  </si>
+  <si>
+    <t>corrEstoqueMais42</t>
+  </si>
+  <si>
+    <t>corrEstoqueMenos42</t>
+  </si>
+  <si>
+    <t>corrEstoqueMais43</t>
+  </si>
+  <si>
+    <t>AnoRelogio4dig_</t>
+  </si>
+  <si>
+    <t>pecaFilaEntForno41</t>
+  </si>
+  <si>
+    <t>40.00</t>
+  </si>
+  <si>
+    <t>40.01</t>
+  </si>
+  <si>
+    <t>40.02</t>
+  </si>
+  <si>
+    <t>40.03</t>
+  </si>
+  <si>
+    <t>40.04</t>
+  </si>
+  <si>
+    <t>40.05</t>
+  </si>
+  <si>
+    <t>40.06</t>
+  </si>
+  <si>
+    <t>40.07</t>
+  </si>
+  <si>
+    <t>40.08</t>
+  </si>
+  <si>
+    <t>40.09</t>
+  </si>
+  <si>
+    <t>40.10</t>
+  </si>
+  <si>
+    <t>40.11</t>
+  </si>
+  <si>
+    <t>41.00</t>
+  </si>
+  <si>
+    <t>41.01</t>
+  </si>
+  <si>
+    <t>41.02</t>
+  </si>
+  <si>
+    <t>41.03</t>
+  </si>
+  <si>
+    <t>41.04</t>
+  </si>
+  <si>
+    <t>41.05</t>
+  </si>
+  <si>
+    <t>41.08</t>
+  </si>
+  <si>
+    <t>41.09</t>
+  </si>
+  <si>
+    <t>41.11</t>
   </si>
 </sst>
 </file>
@@ -1753,4 +2386,1639 @@
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDF405DF-ABF5-4684-BF05-3B01EF699203}">
+  <dimension ref="A1:E95"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="29.42578125" customWidth="1"/>
+    <col min="4" max="4" width="42.7109375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>253</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>336</v>
+      </c>
+      <c r="D1" t="s">
+        <v>147</v>
+      </c>
+      <c r="E1">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>255</v>
+      </c>
+      <c r="B2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" t="s">
+        <v>337</v>
+      </c>
+      <c r="D2" t="s">
+        <v>148</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>257</v>
+      </c>
+      <c r="B3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" t="s">
+        <v>338</v>
+      </c>
+      <c r="D3" t="s">
+        <v>149</v>
+      </c>
+      <c r="E3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>256</v>
+      </c>
+      <c r="B4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C4" t="s">
+        <v>339</v>
+      </c>
+      <c r="D4" t="s">
+        <v>150</v>
+      </c>
+      <c r="E4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>254</v>
+      </c>
+      <c r="B5" t="s">
+        <v>0</v>
+      </c>
+      <c r="C5" t="s">
+        <v>340</v>
+      </c>
+      <c r="D5" t="s">
+        <v>151</v>
+      </c>
+      <c r="E5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>258</v>
+      </c>
+      <c r="B6" t="s">
+        <v>0</v>
+      </c>
+      <c r="C6" t="s">
+        <v>341</v>
+      </c>
+      <c r="D6" t="s">
+        <v>152</v>
+      </c>
+      <c r="E6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>259</v>
+      </c>
+      <c r="B7" t="s">
+        <v>0</v>
+      </c>
+      <c r="C7" t="s">
+        <v>342</v>
+      </c>
+      <c r="D7" t="s">
+        <v>153</v>
+      </c>
+      <c r="E7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>260</v>
+      </c>
+      <c r="B8" t="s">
+        <v>0</v>
+      </c>
+      <c r="C8" t="s">
+        <v>343</v>
+      </c>
+      <c r="D8" t="s">
+        <v>154</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>261</v>
+      </c>
+      <c r="B9" t="s">
+        <v>0</v>
+      </c>
+      <c r="C9" t="s">
+        <v>344</v>
+      </c>
+      <c r="D9" t="s">
+        <v>155</v>
+      </c>
+      <c r="E9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>262</v>
+      </c>
+      <c r="B10" t="s">
+        <v>0</v>
+      </c>
+      <c r="C10" t="s">
+        <v>345</v>
+      </c>
+      <c r="D10" t="s">
+        <v>156</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>263</v>
+      </c>
+      <c r="B11" t="s">
+        <v>0</v>
+      </c>
+      <c r="C11" t="s">
+        <v>346</v>
+      </c>
+      <c r="D11" t="s">
+        <v>157</v>
+      </c>
+      <c r="E11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>264</v>
+      </c>
+      <c r="B12" t="s">
+        <v>0</v>
+      </c>
+      <c r="C12" t="s">
+        <v>347</v>
+      </c>
+      <c r="D12" t="s">
+        <v>158</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>312</v>
+      </c>
+      <c r="B13" t="s">
+        <v>0</v>
+      </c>
+      <c r="C13" t="s">
+        <v>348</v>
+      </c>
+      <c r="D13" t="s">
+        <v>159</v>
+      </c>
+      <c r="E13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>265</v>
+      </c>
+      <c r="B14" t="s">
+        <v>0</v>
+      </c>
+      <c r="C14" t="s">
+        <v>349</v>
+      </c>
+      <c r="D14" t="s">
+        <v>160</v>
+      </c>
+      <c r="E14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>270</v>
+      </c>
+      <c r="B15" t="s">
+        <v>0</v>
+      </c>
+      <c r="C15" t="s">
+        <v>350</v>
+      </c>
+      <c r="D15" t="s">
+        <v>161</v>
+      </c>
+      <c r="E15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>272</v>
+      </c>
+      <c r="B16" t="s">
+        <v>0</v>
+      </c>
+      <c r="C16" t="s">
+        <v>351</v>
+      </c>
+      <c r="D16" t="s">
+        <v>160</v>
+      </c>
+      <c r="E16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>271</v>
+      </c>
+      <c r="B17" t="s">
+        <v>0</v>
+      </c>
+      <c r="C17" t="s">
+        <v>352</v>
+      </c>
+      <c r="D17" t="s">
+        <v>162</v>
+      </c>
+      <c r="E17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>313</v>
+      </c>
+      <c r="B18" t="s">
+        <v>0</v>
+      </c>
+      <c r="C18" t="s">
+        <v>353</v>
+      </c>
+      <c r="D18" t="s">
+        <v>163</v>
+      </c>
+      <c r="E18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>273</v>
+      </c>
+      <c r="B19" t="s">
+        <v>0</v>
+      </c>
+      <c r="C19" t="s">
+        <v>354</v>
+      </c>
+      <c r="D19" t="s">
+        <v>164</v>
+      </c>
+      <c r="E19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>274</v>
+      </c>
+      <c r="B20" t="s">
+        <v>0</v>
+      </c>
+      <c r="C20" t="s">
+        <v>355</v>
+      </c>
+      <c r="D20" t="s">
+        <v>165</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>266</v>
+      </c>
+      <c r="B21" t="s">
+        <v>0</v>
+      </c>
+      <c r="C21" t="s">
+        <v>356</v>
+      </c>
+      <c r="D21" t="s">
+        <v>166</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>314</v>
+      </c>
+      <c r="B22" t="s">
+        <v>0</v>
+      </c>
+      <c r="C22" t="s">
+        <v>5</v>
+      </c>
+      <c r="D22" t="s">
+        <v>167</v>
+      </c>
+      <c r="E22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>315</v>
+      </c>
+      <c r="B23" t="s">
+        <v>0</v>
+      </c>
+      <c r="C23" t="s">
+        <v>168</v>
+      </c>
+      <c r="D23" t="s">
+        <v>167</v>
+      </c>
+      <c r="E23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>316</v>
+      </c>
+      <c r="B24" t="s">
+        <v>0</v>
+      </c>
+      <c r="C24" t="s">
+        <v>169</v>
+      </c>
+      <c r="D24" t="s">
+        <v>167</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>317</v>
+      </c>
+      <c r="B25" t="s">
+        <v>0</v>
+      </c>
+      <c r="C25" t="s">
+        <v>170</v>
+      </c>
+      <c r="D25" t="s">
+        <v>171</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>275</v>
+      </c>
+      <c r="B26" t="s">
+        <v>0</v>
+      </c>
+      <c r="C26" t="s">
+        <v>172</v>
+      </c>
+      <c r="D26" t="s">
+        <v>173</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>318</v>
+      </c>
+      <c r="B27" t="s">
+        <v>0</v>
+      </c>
+      <c r="C27" t="s">
+        <v>174</v>
+      </c>
+      <c r="D27" t="s">
+        <v>175</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>276</v>
+      </c>
+      <c r="B28" t="s">
+        <v>0</v>
+      </c>
+      <c r="C28" t="s">
+        <v>176</v>
+      </c>
+      <c r="D28" t="s">
+        <v>177</v>
+      </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>277</v>
+      </c>
+      <c r="B29" t="s">
+        <v>0</v>
+      </c>
+      <c r="C29" t="s">
+        <v>178</v>
+      </c>
+      <c r="D29" t="s">
+        <v>179</v>
+      </c>
+      <c r="E29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>278</v>
+      </c>
+      <c r="B30" t="s">
+        <v>0</v>
+      </c>
+      <c r="C30" t="s">
+        <v>180</v>
+      </c>
+      <c r="D30" t="s">
+        <v>181</v>
+      </c>
+      <c r="E30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>279</v>
+      </c>
+      <c r="B31" t="s">
+        <v>0</v>
+      </c>
+      <c r="C31" t="s">
+        <v>182</v>
+      </c>
+      <c r="D31" t="s">
+        <v>183</v>
+      </c>
+      <c r="E31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>280</v>
+      </c>
+      <c r="B32" t="s">
+        <v>0</v>
+      </c>
+      <c r="C32" t="s">
+        <v>184</v>
+      </c>
+      <c r="D32" t="s">
+        <v>185</v>
+      </c>
+      <c r="E32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>281</v>
+      </c>
+      <c r="B33" t="s">
+        <v>0</v>
+      </c>
+      <c r="C33" t="s">
+        <v>186</v>
+      </c>
+      <c r="D33" t="s">
+        <v>187</v>
+      </c>
+      <c r="E33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>282</v>
+      </c>
+      <c r="B34" t="s">
+        <v>0</v>
+      </c>
+      <c r="C34" t="s">
+        <v>189</v>
+      </c>
+      <c r="D34" t="s">
+        <v>190</v>
+      </c>
+      <c r="E34">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>283</v>
+      </c>
+      <c r="B35" t="s">
+        <v>0</v>
+      </c>
+      <c r="C35" t="s">
+        <v>191</v>
+      </c>
+      <c r="D35" t="s">
+        <v>192</v>
+      </c>
+      <c r="E35">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>284</v>
+      </c>
+      <c r="B36" t="s">
+        <v>0</v>
+      </c>
+      <c r="C36" t="s">
+        <v>193</v>
+      </c>
+      <c r="D36" t="s">
+        <v>194</v>
+      </c>
+      <c r="E36">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>285</v>
+      </c>
+      <c r="B37" t="s">
+        <v>11</v>
+      </c>
+      <c r="C37" t="s">
+        <v>195</v>
+      </c>
+      <c r="D37" t="s">
+        <v>196</v>
+      </c>
+      <c r="E37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>286</v>
+      </c>
+      <c r="B38" t="s">
+        <v>11</v>
+      </c>
+      <c r="C38" t="s">
+        <v>135</v>
+      </c>
+      <c r="D38" t="s">
+        <v>197</v>
+      </c>
+      <c r="E38">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>335</v>
+      </c>
+      <c r="B39" t="s">
+        <v>11</v>
+      </c>
+      <c r="C39" t="s">
+        <v>198</v>
+      </c>
+      <c r="D39" t="s">
+        <v>199</v>
+      </c>
+      <c r="E39">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>287</v>
+      </c>
+      <c r="B40" t="s">
+        <v>11</v>
+      </c>
+      <c r="C40" t="s">
+        <v>20</v>
+      </c>
+      <c r="D40" t="s">
+        <v>21</v>
+      </c>
+      <c r="E40">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>288</v>
+      </c>
+      <c r="B41" t="s">
+        <v>11</v>
+      </c>
+      <c r="C41" t="s">
+        <v>22</v>
+      </c>
+      <c r="D41" t="s">
+        <v>23</v>
+      </c>
+      <c r="E41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>289</v>
+      </c>
+      <c r="B42" t="s">
+        <v>11</v>
+      </c>
+      <c r="C42" t="s">
+        <v>24</v>
+      </c>
+      <c r="D42" t="s">
+        <v>25</v>
+      </c>
+      <c r="E42">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>90</v>
+      </c>
+      <c r="B43" t="s">
+        <v>11</v>
+      </c>
+      <c r="C43" t="s">
+        <v>26</v>
+      </c>
+      <c r="D43" t="s">
+        <v>27</v>
+      </c>
+      <c r="E43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>91</v>
+      </c>
+      <c r="B44" t="s">
+        <v>11</v>
+      </c>
+      <c r="C44" t="s">
+        <v>28</v>
+      </c>
+      <c r="D44" t="s">
+        <v>29</v>
+      </c>
+      <c r="E44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>92</v>
+      </c>
+      <c r="B45" t="s">
+        <v>11</v>
+      </c>
+      <c r="C45" t="s">
+        <v>30</v>
+      </c>
+      <c r="D45" t="s">
+        <v>200</v>
+      </c>
+      <c r="E45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>334</v>
+      </c>
+      <c r="B46" t="s">
+        <v>11</v>
+      </c>
+      <c r="C46" t="s">
+        <v>32</v>
+      </c>
+      <c r="D46" t="s">
+        <v>201</v>
+      </c>
+      <c r="E46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>92</v>
+      </c>
+      <c r="B47" t="s">
+        <v>11</v>
+      </c>
+      <c r="C47" t="s">
+        <v>202</v>
+      </c>
+      <c r="D47" t="s">
+        <v>31</v>
+      </c>
+      <c r="E47">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>301</v>
+      </c>
+      <c r="B48" t="s">
+        <v>11</v>
+      </c>
+      <c r="C48" t="s">
+        <v>214</v>
+      </c>
+      <c r="D48" t="s">
+        <v>215</v>
+      </c>
+      <c r="E48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>290</v>
+      </c>
+      <c r="B49" t="s">
+        <v>11</v>
+      </c>
+      <c r="C49" t="s">
+        <v>203</v>
+      </c>
+      <c r="D49" t="s">
+        <v>33</v>
+      </c>
+      <c r="E49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>302</v>
+      </c>
+      <c r="B50" t="s">
+        <v>11</v>
+      </c>
+      <c r="C50" t="s">
+        <v>216</v>
+      </c>
+      <c r="D50" t="s">
+        <v>217</v>
+      </c>
+      <c r="E50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>93</v>
+      </c>
+      <c r="B51" t="s">
+        <v>11</v>
+      </c>
+      <c r="C51" t="s">
+        <v>34</v>
+      </c>
+      <c r="D51" t="s">
+        <v>35</v>
+      </c>
+      <c r="E51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B52" t="s">
+        <v>11</v>
+      </c>
+      <c r="C52" t="s">
+        <v>218</v>
+      </c>
+      <c r="D52" t="s">
+        <v>188</v>
+      </c>
+      <c r="E52">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>291</v>
+      </c>
+      <c r="B53" t="s">
+        <v>11</v>
+      </c>
+      <c r="C53" t="s">
+        <v>36</v>
+      </c>
+      <c r="D53" t="s">
+        <v>204</v>
+      </c>
+      <c r="E53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>267</v>
+      </c>
+      <c r="B54" t="s">
+        <v>11</v>
+      </c>
+      <c r="C54" t="s">
+        <v>38</v>
+      </c>
+      <c r="D54" t="s">
+        <v>205</v>
+      </c>
+      <c r="E54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>268</v>
+      </c>
+      <c r="B55" t="s">
+        <v>11</v>
+      </c>
+      <c r="C55" t="s">
+        <v>42</v>
+      </c>
+      <c r="D55" t="s">
+        <v>206</v>
+      </c>
+      <c r="E55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>269</v>
+      </c>
+      <c r="B56" t="s">
+        <v>11</v>
+      </c>
+      <c r="C56" t="s">
+        <v>46</v>
+      </c>
+      <c r="D56" t="s">
+        <v>207</v>
+      </c>
+      <c r="E56">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>292</v>
+      </c>
+      <c r="B57" t="s">
+        <v>11</v>
+      </c>
+      <c r="C57" t="s">
+        <v>50</v>
+      </c>
+      <c r="D57" t="s">
+        <v>208</v>
+      </c>
+      <c r="E57">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>293</v>
+      </c>
+      <c r="B58" t="s">
+        <v>11</v>
+      </c>
+      <c r="C58" t="s">
+        <v>209</v>
+      </c>
+      <c r="D58" t="s">
+        <v>210</v>
+      </c>
+      <c r="E58">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>319</v>
+      </c>
+      <c r="B59" t="s">
+        <v>11</v>
+      </c>
+      <c r="C59" t="s">
+        <v>211</v>
+      </c>
+      <c r="D59" t="s">
+        <v>188</v>
+      </c>
+      <c r="E59">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B60" t="s">
+        <v>11</v>
+      </c>
+      <c r="C60" t="s">
+        <v>212</v>
+      </c>
+      <c r="D60" t="s">
+        <v>188</v>
+      </c>
+      <c r="E60">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>294</v>
+      </c>
+      <c r="B61" t="s">
+        <v>11</v>
+      </c>
+      <c r="C61" t="s">
+        <v>52</v>
+      </c>
+      <c r="D61" t="s">
+        <v>53</v>
+      </c>
+      <c r="E61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>295</v>
+      </c>
+      <c r="B62" t="s">
+        <v>11</v>
+      </c>
+      <c r="C62" t="s">
+        <v>54</v>
+      </c>
+      <c r="D62" t="s">
+        <v>55</v>
+      </c>
+      <c r="E62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>296</v>
+      </c>
+      <c r="B63" t="s">
+        <v>11</v>
+      </c>
+      <c r="C63" t="s">
+        <v>56</v>
+      </c>
+      <c r="D63" t="s">
+        <v>57</v>
+      </c>
+      <c r="E63">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>297</v>
+      </c>
+      <c r="B64" t="s">
+        <v>11</v>
+      </c>
+      <c r="C64" t="s">
+        <v>58</v>
+      </c>
+      <c r="D64" t="s">
+        <v>59</v>
+      </c>
+      <c r="E64">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>299</v>
+      </c>
+      <c r="B65" t="s">
+        <v>11</v>
+      </c>
+      <c r="C65" t="s">
+        <v>60</v>
+      </c>
+      <c r="D65" t="s">
+        <v>213</v>
+      </c>
+      <c r="E65">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>104</v>
+      </c>
+      <c r="B66" t="s">
+        <v>11</v>
+      </c>
+      <c r="C66" t="s">
+        <v>62</v>
+      </c>
+      <c r="D66" t="s">
+        <v>63</v>
+      </c>
+      <c r="E66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>300</v>
+      </c>
+      <c r="B67" t="s">
+        <v>11</v>
+      </c>
+      <c r="C67" t="s">
+        <v>64</v>
+      </c>
+      <c r="D67" t="s">
+        <v>65</v>
+      </c>
+      <c r="E67">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>104</v>
+      </c>
+      <c r="B68" t="s">
+        <v>11</v>
+      </c>
+      <c r="C68" t="s">
+        <v>66</v>
+      </c>
+      <c r="D68" t="s">
+        <v>63</v>
+      </c>
+      <c r="E68">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>320</v>
+      </c>
+      <c r="B69" t="s">
+        <v>0</v>
+      </c>
+      <c r="C69" t="s">
+        <v>219</v>
+      </c>
+      <c r="D69" t="s">
+        <v>220</v>
+      </c>
+      <c r="E69">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>303</v>
+      </c>
+      <c r="B70" t="s">
+        <v>0</v>
+      </c>
+      <c r="C70" t="s">
+        <v>221</v>
+      </c>
+      <c r="D70" t="s">
+        <v>222</v>
+      </c>
+      <c r="E70">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>321</v>
+      </c>
+      <c r="B71" t="s">
+        <v>0</v>
+      </c>
+      <c r="C71" t="s">
+        <v>223</v>
+      </c>
+      <c r="D71" t="s">
+        <v>220</v>
+      </c>
+      <c r="E71">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>304</v>
+      </c>
+      <c r="B72" t="s">
+        <v>0</v>
+      </c>
+      <c r="C72" t="s">
+        <v>224</v>
+      </c>
+      <c r="D72" t="s">
+        <v>225</v>
+      </c>
+      <c r="E72">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>322</v>
+      </c>
+      <c r="B73" t="s">
+        <v>0</v>
+      </c>
+      <c r="C73" t="s">
+        <v>226</v>
+      </c>
+      <c r="D73" t="s">
+        <v>220</v>
+      </c>
+      <c r="E73">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>305</v>
+      </c>
+      <c r="B74" t="s">
+        <v>0</v>
+      </c>
+      <c r="C74" t="s">
+        <v>227</v>
+      </c>
+      <c r="D74" t="s">
+        <v>228</v>
+      </c>
+      <c r="E74">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>306</v>
+      </c>
+      <c r="B75" t="s">
+        <v>0</v>
+      </c>
+      <c r="C75" t="s">
+        <v>229</v>
+      </c>
+      <c r="D75" t="s">
+        <v>230</v>
+      </c>
+      <c r="E75">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>307</v>
+      </c>
+      <c r="B76" t="s">
+        <v>0</v>
+      </c>
+      <c r="C76" t="s">
+        <v>231</v>
+      </c>
+      <c r="D76" t="s">
+        <v>232</v>
+      </c>
+      <c r="E76">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>266</v>
+      </c>
+      <c r="B77" t="s">
+        <v>0</v>
+      </c>
+      <c r="C77" t="s">
+        <v>233</v>
+      </c>
+      <c r="D77" t="s">
+        <v>234</v>
+      </c>
+      <c r="E77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>323</v>
+      </c>
+      <c r="B78" t="s">
+        <v>0</v>
+      </c>
+      <c r="C78" t="s">
+        <v>235</v>
+      </c>
+      <c r="D78" t="s">
+        <v>236</v>
+      </c>
+      <c r="E78">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>308</v>
+      </c>
+      <c r="B79" t="s">
+        <v>0</v>
+      </c>
+      <c r="C79" t="s">
+        <v>67</v>
+      </c>
+      <c r="D79" t="s">
+        <v>237</v>
+      </c>
+      <c r="E79">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>324</v>
+      </c>
+      <c r="B80" t="s">
+        <v>0</v>
+      </c>
+      <c r="C80" t="s">
+        <v>238</v>
+      </c>
+      <c r="D80" t="s">
+        <v>239</v>
+      </c>
+      <c r="E80">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>324</v>
+      </c>
+      <c r="B81" t="s">
+        <v>0</v>
+      </c>
+      <c r="C81" t="s">
+        <v>240</v>
+      </c>
+      <c r="D81" t="s">
+        <v>239</v>
+      </c>
+      <c r="E81">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>325</v>
+      </c>
+      <c r="B82" t="s">
+        <v>0</v>
+      </c>
+      <c r="C82" t="s">
+        <v>241</v>
+      </c>
+      <c r="D82" t="s">
+        <v>236</v>
+      </c>
+      <c r="E82">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>326</v>
+      </c>
+      <c r="B83" t="s">
+        <v>0</v>
+      </c>
+      <c r="C83" t="s">
+        <v>242</v>
+      </c>
+      <c r="D83" t="s">
+        <v>239</v>
+      </c>
+      <c r="E83">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>327</v>
+      </c>
+      <c r="B84" t="s">
+        <v>0</v>
+      </c>
+      <c r="C84" t="s">
+        <v>243</v>
+      </c>
+      <c r="D84" t="s">
+        <v>236</v>
+      </c>
+      <c r="E84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>328</v>
+      </c>
+      <c r="B85" t="s">
+        <v>0</v>
+      </c>
+      <c r="C85" t="s">
+        <v>244</v>
+      </c>
+      <c r="D85" t="s">
+        <v>245</v>
+      </c>
+      <c r="E85">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>329</v>
+      </c>
+      <c r="B86" t="s">
+        <v>0</v>
+      </c>
+      <c r="C86" t="s">
+        <v>246</v>
+      </c>
+      <c r="D86" t="s">
+        <v>247</v>
+      </c>
+      <c r="E86">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>330</v>
+      </c>
+      <c r="B87" t="s">
+        <v>0</v>
+      </c>
+      <c r="C87" t="s">
+        <v>248</v>
+      </c>
+      <c r="D87" t="s">
+        <v>245</v>
+      </c>
+      <c r="E87">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>331</v>
+      </c>
+      <c r="B88" t="s">
+        <v>0</v>
+      </c>
+      <c r="C88" t="s">
+        <v>249</v>
+      </c>
+      <c r="D88" t="s">
+        <v>247</v>
+      </c>
+      <c r="E88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>332</v>
+      </c>
+      <c r="B89" t="s">
+        <v>0</v>
+      </c>
+      <c r="C89" t="s">
+        <v>250</v>
+      </c>
+      <c r="D89" t="s">
+        <v>245</v>
+      </c>
+      <c r="E89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>333</v>
+      </c>
+      <c r="B90" t="s">
+        <v>0</v>
+      </c>
+      <c r="C90" t="s">
+        <v>251</v>
+      </c>
+      <c r="D90" t="s">
+        <v>247</v>
+      </c>
+      <c r="E90">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>310</v>
+      </c>
+      <c r="B91" t="s">
+        <v>0</v>
+      </c>
+      <c r="C91" t="s">
+        <v>69</v>
+      </c>
+      <c r="D91" t="s">
+        <v>70</v>
+      </c>
+      <c r="E91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>309</v>
+      </c>
+      <c r="B92" t="s">
+        <v>0</v>
+      </c>
+      <c r="C92" t="s">
+        <v>71</v>
+      </c>
+      <c r="D92" t="s">
+        <v>72</v>
+      </c>
+      <c r="E92">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>311</v>
+      </c>
+      <c r="B93" t="s">
+        <v>0</v>
+      </c>
+      <c r="C93" t="s">
+        <v>73</v>
+      </c>
+      <c r="D93" t="s">
+        <v>74</v>
+      </c>
+      <c r="E93">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>298</v>
+      </c>
+      <c r="B94" t="s">
+        <v>0</v>
+      </c>
+      <c r="C94" t="s">
+        <v>75</v>
+      </c>
+      <c r="D94" t="s">
+        <v>252</v>
+      </c>
+      <c r="E94">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D95" t="s">
+        <v>188</v>
+      </c>
+      <c r="E95">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A1:E96">
+    <sortCondition ref="C1:C96"/>
+  </sortState>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EEE1EC77-3C92-4DB9-8C7A-2336A7DBB7A7}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C5BBB77-C3B8-4E30-8FB9-81E5C3784589}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
 </file>
--- a/clp/qualidade/tagPrensa.xlsx
+++ b/clp/qualidade/tagPrensa.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\hostLinkOmron\hotsLinkOmron\clp\qualidade\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA8E2E80-AD3C-4911-8F9A-0E38535D2B91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB58C96F-D945-4487-9AF3-E5DE81D26DEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1870" uniqueCount="706">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1874" uniqueCount="711">
   <si>
     <t>prensa29</t>
   </si>
@@ -2055,15 +2055,6 @@
     <t>Segundo</t>
   </si>
   <si>
-    <t>D321</t>
-  </si>
-  <si>
-    <t>D323</t>
-  </si>
-  <si>
-    <t>D325</t>
-  </si>
-  <si>
     <t>PONTEIRO INICIO</t>
   </si>
   <si>
@@ -2158,6 +2149,30 @@
   </si>
   <si>
     <t>minuto e segundo clp</t>
+  </si>
+  <si>
+    <t>D3002</t>
+  </si>
+  <si>
+    <t>D3003</t>
+  </si>
+  <si>
+    <t>D3004</t>
+  </si>
+  <si>
+    <t>D3005</t>
+  </si>
+  <si>
+    <t>D3006</t>
+  </si>
+  <si>
+    <t>D3001...D3006</t>
+  </si>
+  <si>
+    <t>D3007</t>
+  </si>
+  <si>
+    <t>D3008...D3007</t>
   </si>
 </sst>
 </file>
@@ -2242,9 +2257,6 @@
   <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2253,6 +2265,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2812,20 +2827,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="6" t="s">
         <v>531</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="H1" s="2" t="s">
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="H1" s="6" t="s">
         <v>530</v>
       </c>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
+      <c r="L1" s="6"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
@@ -10990,8 +11005,8 @@
     <col min="4" max="4" width="20.28515625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="15" customWidth="1"/>
-    <col min="7" max="7" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -11006,44 +11021,44 @@
       <c r="A2" t="s">
         <v>648</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>584</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>651</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>659</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="3" t="s">
         <v>663</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="3" t="s">
         <v>664</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>652</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="2" t="s">
         <v>585</v>
       </c>
-      <c r="H4" s="5" t="s">
-        <v>590</v>
-      </c>
-      <c r="I4" s="5" t="s">
+      <c r="H4" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="I4" s="4" t="s">
         <v>665</v>
       </c>
     </row>
@@ -11051,16 +11066,16 @@
       <c r="A5" t="s">
         <v>653</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="2" t="s">
         <v>660</v>
       </c>
-      <c r="H5" s="5" t="s">
-        <v>671</v>
-      </c>
-      <c r="I5" s="5" t="s">
+      <c r="H5" s="4" t="s">
+        <v>703</v>
+      </c>
+      <c r="I5" s="4" t="s">
         <v>666</v>
       </c>
     </row>
@@ -11068,16 +11083,16 @@
       <c r="A6" t="s">
         <v>654</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="2" t="s">
         <v>586</v>
       </c>
-      <c r="H6" s="5" t="s">
-        <v>591</v>
-      </c>
-      <c r="I6" s="5" t="s">
+      <c r="H6" s="4" t="s">
+        <v>704</v>
+      </c>
+      <c r="I6" s="4" t="s">
         <v>667</v>
       </c>
     </row>
@@ -11085,62 +11100,62 @@
       <c r="A7" t="s">
         <v>655</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="2" t="s">
         <v>661</v>
       </c>
-      <c r="H7" s="5" t="s">
-        <v>672</v>
-      </c>
-      <c r="I7" s="5" t="s">
+      <c r="H7" s="4" t="s">
+        <v>705</v>
+      </c>
+      <c r="I7" s="4" t="s">
         <v>668</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>674</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>675</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>592</v>
-      </c>
-      <c r="I8" s="5" t="s">
+        <v>671</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>672</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>706</v>
+      </c>
+      <c r="I8" s="4" t="s">
         <v>669</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>677</v>
-      </c>
-      <c r="C9" s="6" t="s">
+        <v>674</v>
+      </c>
+      <c r="C9" s="5" t="s">
         <v>589</v>
       </c>
-      <c r="H9" s="5" t="s">
-        <v>673</v>
-      </c>
-      <c r="I9" s="5" t="s">
+      <c r="H9" s="4" t="s">
+        <v>707</v>
+      </c>
+      <c r="I9" s="4" t="s">
         <v>670</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="F11" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="G11" t="s">
         <v>165</v>
       </c>
-      <c r="H11" s="5" t="s">
+      <c r="H11" s="4" t="s">
         <v>581</v>
       </c>
-      <c r="I11" s="5" t="s">
+      <c r="I11" s="4" t="s">
         <v>656</v>
       </c>
       <c r="J11" t="s">
@@ -11154,28 +11169,28 @@
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
       <c r="F12" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="G12" t="s">
         <v>589</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
       <c r="F13" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="G13" t="s">
         <v>159</v>
       </c>
-      <c r="H13" s="5" t="s">
+      <c r="H13" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="I13" s="5" t="s">
+      <c r="I13" s="4" t="s">
         <v>581</v>
       </c>
       <c r="J13" t="s">
@@ -11189,48 +11204,62 @@
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
       <c r="F15" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="G15" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="H15" t="s">
+        <v>674</v>
+      </c>
+      <c r="I15" t="s">
         <v>677</v>
       </c>
-      <c r="I15" t="s">
-        <v>680</v>
-      </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
       <c r="F16" t="s">
         <v>159</v>
       </c>
       <c r="G16" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
       <c r="H16" t="s">
         <v>658</v>
       </c>
       <c r="I16" t="s">
-        <v>682</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B18" s="3"/>
-      <c r="C18" s="3"/>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B19" s="3"/>
-      <c r="C19" s="3"/>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="F17" t="s">
+        <v>162</v>
+      </c>
+      <c r="G17" t="s">
+        <v>708</v>
+      </c>
+      <c r="H17" t="s">
+        <v>709</v>
+      </c>
+      <c r="I17" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="B23" t="s">
         <v>14</v>
@@ -11239,15 +11268,15 @@
         <v>165</v>
       </c>
       <c r="D23" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="E23">
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="B24" t="s">
         <v>14</v>
@@ -11256,15 +11285,15 @@
         <v>581</v>
       </c>
       <c r="D24" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="E24">
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="B25" t="s">
         <v>14</v>
@@ -11273,15 +11302,15 @@
         <v>656</v>
       </c>
       <c r="D25" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="E25">
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="B26" t="s">
         <v>14</v>
@@ -11290,15 +11319,15 @@
         <v>582</v>
       </c>
       <c r="D26" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="E26">
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="B27" t="s">
         <v>14</v>
@@ -11307,15 +11336,15 @@
         <v>657</v>
       </c>
       <c r="D27" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="E27">
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="B28" t="s">
         <v>14</v>
@@ -11324,15 +11353,15 @@
         <v>583</v>
       </c>
       <c r="D28" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="E28">
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="B29" t="s">
         <v>14</v>
@@ -11341,58 +11370,58 @@
         <v>658</v>
       </c>
       <c r="D29" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="E29">
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
+        <v>696</v>
+      </c>
+      <c r="B30" t="s">
+        <v>14</v>
+      </c>
+      <c r="C30" t="s">
+        <v>687</v>
+      </c>
+      <c r="D30" t="s">
+        <v>688</v>
+      </c>
+      <c r="E30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
         <v>699</v>
       </c>
-      <c r="B30" t="s">
-        <v>14</v>
-      </c>
-      <c r="C30" t="s">
-        <v>690</v>
-      </c>
-      <c r="D30" t="s">
-        <v>691</v>
-      </c>
-      <c r="E30">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
+      <c r="B31" t="s">
+        <v>14</v>
+      </c>
+      <c r="C31" t="s">
+        <v>697</v>
+      </c>
+      <c r="D31" t="s">
+        <v>698</v>
+      </c>
+      <c r="E31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>700</v>
+      </c>
+      <c r="B32" t="s">
+        <v>14</v>
+      </c>
+      <c r="C32" t="s">
+        <v>701</v>
+      </c>
+      <c r="D32" t="s">
         <v>702</v>
-      </c>
-      <c r="B31" t="s">
-        <v>14</v>
-      </c>
-      <c r="C31" t="s">
-        <v>700</v>
-      </c>
-      <c r="D31" t="s">
-        <v>701</v>
-      </c>
-      <c r="E31">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>703</v>
-      </c>
-      <c r="B32" t="s">
-        <v>14</v>
-      </c>
-      <c r="C32" t="s">
-        <v>704</v>
-      </c>
-      <c r="D32" t="s">
-        <v>705</v>
       </c>
       <c r="E32">
         <v>0</v>

--- a/clp/qualidade/tagPrensa.xlsx
+++ b/clp/qualidade/tagPrensa.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\hostLinkOmron\hotsLinkOmron\clp\qualidade\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB58C96F-D945-4487-9AF3-E5DE81D26DEF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{297A6F92-EE4A-41EF-9F1F-E0979067D98D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
